--- a/data/raw/gdp_qoq.xlsx
+++ b/data/raw/gdp_qoq.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,19 +421,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B2" t="n">
@@ -455,7 +441,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B3" t="n">
@@ -463,7 +449,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B4" t="n">
@@ -471,7 +457,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B5" t="n">
@@ -479,7 +465,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B6" t="n">
@@ -487,7 +473,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B7" t="n">
@@ -495,7 +481,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B8" t="n">
@@ -503,7 +489,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B9" t="n">
@@ -511,7 +497,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B10" t="n">
@@ -519,7 +505,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B11" t="n">
@@ -527,7 +513,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B12" t="n">
@@ -535,7 +521,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B13" t="n">
@@ -543,7 +529,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B14" t="n">
@@ -551,7 +537,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B15" t="n">
@@ -559,7 +545,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B16" t="n">
@@ -567,7 +553,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B17" t="n">
@@ -575,7 +561,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B18" t="n">
@@ -583,7 +569,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B19" t="n">
@@ -591,7 +577,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B20" t="n">
@@ -599,7 +585,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B21" t="n">
@@ -607,7 +593,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B22" t="n">
@@ -615,7 +601,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B23" t="n">
@@ -623,7 +609,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B24" t="n">
@@ -631,7 +617,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B25" t="n">
@@ -639,7 +625,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B26" t="n">
@@ -647,7 +633,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B27" t="n">
@@ -655,7 +641,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B28" t="n">
@@ -663,7 +649,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B29" t="n">
@@ -671,7 +657,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B30" t="n">
@@ -679,7 +665,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B31" t="n">
@@ -687,7 +673,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B32" t="n">
@@ -695,7 +681,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B33" t="n">
@@ -703,7 +689,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B34" t="n">
@@ -711,7 +697,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B35" t="n">
@@ -719,7 +705,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B36" t="n">
@@ -727,7 +713,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B37" t="n">
@@ -735,7 +721,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B38" t="n">
@@ -743,7 +729,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B39" t="n">
@@ -751,7 +737,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B40" t="n">
@@ -759,7 +745,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B41" t="n">
@@ -767,7 +753,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B42" t="n">
@@ -775,7 +761,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B43" t="n">
@@ -783,7 +769,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B44" t="n">
@@ -791,7 +777,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B45" t="n">
@@ -799,7 +785,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B46" t="n">
@@ -807,7 +793,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B47" t="n">
@@ -815,7 +801,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B48" t="n">
@@ -823,7 +809,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B49" t="n">
@@ -831,7 +817,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B50" t="n">
@@ -839,7 +825,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B51" t="n">
@@ -847,7 +833,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B52" t="n">
@@ -855,7 +841,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B53" t="n">
@@ -863,7 +849,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B54" t="n">
@@ -871,7 +857,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B55" t="n">
@@ -879,7 +865,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B56" t="n">
@@ -887,7 +873,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B57" t="n">
@@ -895,7 +881,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B58" t="n">
@@ -903,7 +889,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B59" t="n">
@@ -911,7 +897,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B60" t="n">
@@ -919,7 +905,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B61" t="n">
@@ -927,7 +913,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B62" t="n">
@@ -935,7 +921,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B63" t="n">
@@ -943,7 +929,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B64" t="n">
@@ -951,7 +937,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B65" t="n">
@@ -959,7 +945,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B66" t="n">
@@ -967,7 +953,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B67" t="n">
@@ -975,7 +961,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B68" t="n">
@@ -983,7 +969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B69" t="n">
@@ -991,7 +977,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B70" t="n">
@@ -999,7 +985,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B71" t="n">
@@ -1007,7 +993,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B72" t="n">
@@ -1015,7 +1001,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B73" t="n">
@@ -1023,7 +1009,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B74" t="n">
@@ -1031,7 +1017,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B75" t="n">
@@ -1039,7 +1025,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B76" t="n">
@@ -1047,7 +1033,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B77" t="n">
@@ -1055,7 +1041,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B78" t="n">
@@ -1063,7 +1049,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B79" t="n">
@@ -1071,7 +1057,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B80" t="n">
@@ -1079,7 +1065,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B81" t="n">
@@ -1087,7 +1073,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B82" t="n">
@@ -1095,7 +1081,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B83" t="n">
@@ -1103,7 +1089,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B84" t="n">
@@ -1111,7 +1097,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B85" t="n">
@@ -1119,7 +1105,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B86" t="n">
@@ -1127,7 +1113,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B87" t="n">
@@ -1135,7 +1121,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B88" t="n">
@@ -1143,7 +1129,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B89" t="n">
@@ -1151,7 +1137,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B90" t="n">
@@ -1159,7 +1145,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B91" t="n">
@@ -1167,7 +1153,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B92" t="n">
@@ -1175,7 +1161,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B93" t="n">
@@ -1183,7 +1169,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B94" t="n">
@@ -1191,7 +1177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B95" t="n">
@@ -1199,7 +1185,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B96" t="n">
@@ -1207,7 +1193,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B97" t="n">
@@ -1215,7 +1201,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B98" t="n">
@@ -1223,7 +1209,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B99" t="n">
@@ -1231,7 +1217,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B100" t="n">
@@ -1239,7 +1225,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B101" t="n">
@@ -1247,7 +1233,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B102" t="n">
@@ -1255,7 +1241,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B103" t="n">
@@ -1263,7 +1249,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B104" t="n">
@@ -1271,7 +1257,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B105" t="n">
@@ -1279,7 +1265,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B106" t="n">
@@ -1287,7 +1273,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B107" t="n">
@@ -1295,7 +1281,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B108" t="n">
@@ -1303,7 +1289,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B109" t="n">
@@ -1311,7 +1297,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B110" t="n">
@@ -1319,7 +1305,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B111" t="n">
@@ -1327,7 +1313,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B112" t="n">
@@ -1335,7 +1321,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B113" t="n">
@@ -1343,7 +1329,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B114" t="n">
@@ -1351,7 +1337,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B115" t="n">
@@ -1359,7 +1345,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B116" t="n">
@@ -1367,7 +1353,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B117" t="n">
@@ -1375,7 +1361,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B118" t="n">
@@ -1383,7 +1369,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B119" t="n">
@@ -1391,7 +1377,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B120" t="n">
@@ -1399,7 +1385,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B121" t="n">
@@ -1407,7 +1393,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B122" t="n">
@@ -1415,7 +1401,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B123" t="n">
@@ -1423,7 +1409,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B124" t="n">
@@ -1431,7 +1417,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B125" t="n">
